--- a/CryoGrid/CryoGridCommunity_results/templates/restart_broken/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/restart_broken/TILE_LOOP_NEXT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\restart_broken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687FA32F-57A1-4C33-82FD-12DC084E3F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44176BEE-483D-4F54-849D-E02580831757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -614,7 +614,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">

--- a/CryoGrid/CryoGridCommunity_results/templates/restart_broken/TILE_LOOP_NEXT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/restart_broken/TILE_LOOP_NEXT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\restart_broken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44176BEE-483D-4F54-849D-E02580831757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF4965E-7C3E-4035-9FB7-63EA369A3BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>FORCING_seb_mat</t>
   </si>
   <si>
-    <t>OUT_last_timestep</t>
-  </si>
-  <si>
     <t>restart_OUT_last_timestep</t>
   </si>
   <si>
@@ -97,6 +94,9 @@
   </si>
   <si>
     <t>TILE_1D</t>
+  </si>
+  <si>
+    <t>OUT_last_timestep_VP</t>
   </si>
 </sst>
 </file>
@@ -497,7 +497,7 @@
     </row>
     <row r="3" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -509,17 +509,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -530,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -552,12 +552,12 @@
     </row>
     <row r="10" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -586,7 +586,7 @@
     </row>
     <row r="17" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
@@ -598,7 +598,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -625,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
